--- a/outputs/EMS upgrade output - pump_centrifugal.xlsx
+++ b/outputs/EMS upgrade output - pump_centrifugal.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,74 +471,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t>:---</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t>:---</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>:--- *</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t>:---</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t>:---</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t>:---</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller material loss from particle impingement creates imbalance and progressive vibration </t>
+          <t>:---</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller thickness measurement [Y/N]; Pump vibration monitoring [Y/N]; Erosion rate analysis [Y/N] </t>
+          <t>:---</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t xml:space="preserve">TBD </t>
+          <t>:---</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t>:---</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the non-drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cyclic hydraulic loading initiates vane root fatigue cracks causing imbalance and vibration </t>
+          <t xml:space="preserve">Degradation of rolling elements increases radial clearance, causing abnormal vibration </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration spectrum analysis [Y/N]; Impeller NDT inspection [Y/N]; Operating range verification [Y/N] </t>
+          <t xml:space="preserve">Bearing housing vibration levels within acceptable limits [Y/N] </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -568,29 +568,29 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the non-drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -600,17 +600,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 Cavitation </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cavitation bubble collapse on impeller surface causes pitting and mass loss with severe vibration </t>
+          <t xml:space="preserve">Incorrect internal clearances due to thermal growth or tolerance stack-up generating abnormal vibration </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">NPSH margin verification [Y/N]; Suction pressure monitoring [Y/N]; Impeller cavitation inspection [Y/N] </t>
+          <t xml:space="preserve">Bearing housing vibration levels within acceptable limits [Y/N] </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -620,29 +620,29 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the non-drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -652,17 +652,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller loose on shaft due to keyway wear or thread loosening creates rotational imbalance </t>
+          <t xml:space="preserve">Subsurface spalling of bearing raceways due to cyclic loading exceeding endurance limit </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller fit verification [Y/N]; Key condition inspection [Y/N]; Lock nut torque check [Y/N] </t>
+          <t xml:space="preserve">Bearing housing vibration levels within acceptable limits [Y/N] </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -672,49 +672,49 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the non-drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Particle erosion enlarges impeller vane passages, reducing pump head and flow capacity </t>
+          <t xml:space="preserve">Abrasive wear of rolling elements and cage generates audible high-frequency noise </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Performance curve trending [Y/N]; Impeller clearance measurement [Y/N]; Flow vs head monitoring [Y/N] </t>
+          <t xml:space="preserve">Bearing housing noise levels abnormal during operation [Y/N] </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,49 +724,49 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the non-drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chemical corrosion thins impeller vanes, altering hydraulic profile and degrading pump performance </t>
+          <t xml:space="preserve">Cage deformation or rolling element skidding causes intermittent sticking and periodic noise </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller condition inspection [Y/N]; Process fluid analysis [Y/N]; Performance trend monitoring [Y/N] </t>
+          <t xml:space="preserve">Bearing housing noise levels abnormal during operation [Y/N] </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -776,49 +776,49 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the non-drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">OHE - Overheating </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 Cavitation </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cavitation erosion modifies impeller geometry causing head degradation and efficiency loss </t>
+          <t xml:space="preserve">Excessive friction from degraded rolling elements generates heat </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suction pressure verification [Y/N]; NPSH available calculation [Y/N]; Pump differential pressure check [Y/N] </t>
+          <t xml:space="preserve">Bearing housing temperature exceeds normal range [Y/N] </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -828,49 +828,49 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the non-drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">OHE - Overheating </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wear reduces impeller vane thickness and diameter, decreasing pump hydraulic performance </t>
+          <t xml:space="preserve">Ingress of contaminants into grease/lubricant increases frictional torque and temperature </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller dimensional check [Y/N]; Pump operating hours tracking [Y/N]; Wear rate calculation [Y/N] </t>
+          <t xml:space="preserve">Bearing housing temperature exceeds normal range [Y/N] </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -880,49 +880,49 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the non-drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 Cavitation </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cavitation bubble implosion generates characteristic crackling/gravel-like audible noise </t>
+          <t xml:space="preserve">Wear of the bearing housing seal allows lubricating oil/grease to leak externally </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic cavitation detection [Y/N]; Suction strainer condition check [Y/N]; Pump flow rate verification [Y/N] </t>
+          <t xml:space="preserve">Oil/grease residue visible on bearing housing or surrounding area [Y/N] </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -932,49 +932,49 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the non-drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking/Seizure </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foreign object trapped between impeller and casing generates metallic grinding/tapping noise </t>
+          <t xml:space="preserve">Distortion of bearing housing sealing surfaces prevents proper sealing </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Suction strainer integrity check [Y/N]; Impeller visual inspection [Y/N]; Debris trap cleaning [Y/N] </t>
+          <t xml:space="preserve">Oil/grease residue visible on bearing housing or surrounding area [Y/N] </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -984,49 +984,49 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the non-drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/Alignment failure </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller rubbing against stationary wear rings due to insufficient clearance generates screeching noise </t>
+          <t xml:space="preserve">Increased bearing clearance due to wear alters shaft position, affecting monitoring parameters </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Running clearance measurement [Y/N]; Wear ring condition check [Y/N]; Rotor axial position verification [Y/N] </t>
+          <t xml:space="preserve">Bearing condition monitoring parameters deviate from baseline [Y/N] </t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1036,49 +1036,49 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>NDE Bearing Failure *</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the non-drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erosive wear creates rough impeller surface causing fluid turbulence noise during operation </t>
+          <t xml:space="preserve">Contamination degrades lubricant properties, altering temperature and vibration trends </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller surface inspection [Y/N]; Flow turbulence analysis [Y/N]; Erosion protection coating check [Y/N] </t>
+          <t xml:space="preserve">Bearing condition monitoring parameters deviate from baseline [Y/N] </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1088,34 +1088,34 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Advanced impeller wear reduces pump efficiency; excess energy dissipates as heat, raising pump temperature </t>
+          <t xml:space="preserve">Degradation of rolling elements increases radial clearance, causing abnormal vibration </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Efficiency trend analysis [Y/N]; Impeller condition inspection [Y/N]; Pump temperature monitoring [Y/N] </t>
+          <t xml:space="preserve">Bearing housing vibration levels within acceptable limits [Y/N] </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1140,49 +1140,49 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 Cavitation </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cavitation causes local fluid compression heating at bubble collapse zone, raising pump case temperature </t>
+          <t xml:space="preserve">Misalignment between pump and driver shafts induces a moment on the DE bearing </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cavitation detection monitoring [Y/N]; Pump case temperature check [Y/N]; Flow rate optimization [Y/N] </t>
+          <t xml:space="preserve">Bearing housing vibration levels within acceptable limits [Y/N] </t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1192,49 +1192,49 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1 Blockage/plugged </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller vane passage blockage reduces flow; fluid recirculates and heats up within pump casing </t>
+          <t xml:space="preserve">Subsurface spalling of bearing raceways due to cyclic loading exceeding endurance limit </t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Inlet strainer cleaning [Y/N]; Pump flow monitoring [Y/N]; Impeller passage inspection [Y/N] </t>
+          <t xml:space="preserve">Bearing housing vibration levels within acceptable limits [Y/N] </t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1244,49 +1244,49 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking/Seizure </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller rubbing against casing due to thermal expansion generates frictional heat </t>
+          <t xml:space="preserve">Abrasive wear of rolling elements and cage generates audible high-frequency noise </t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Running clearance check [Y/N]; Thermal growth calculation [Y/N]; Warm-up procedure compliance [Y/N] </t>
+          <t xml:space="preserve">Bearing housing noise levels abnormal during operation [Y/N] </t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1296,49 +1296,49 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Corrosive attack penetrates impeller disc/shroud, creating through-wall leak path to casing joint </t>
+          <t xml:space="preserve">Cage deformation or rolling element skidding causes intermittent sticking and periodic noise </t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller corrosion inspection [Y/N]; Casing drain check [Y/N]; Chemical treatment verification [Y/N] </t>
+          <t xml:space="preserve">Bearing housing noise levels abnormal during operation [Y/N] </t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1348,49 +1348,49 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">OHE - Overheating </t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Erosive wear creates hole through impeller shroud; internal recirculation leads to casing leak </t>
+          <t xml:space="preserve">Excessive friction from degraded rolling elements generates heat </t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">UT thickness measurement [Y/N]; Casing drain monitoring [Y/N]; Erosion rate calculation [Y/N] </t>
+          <t xml:space="preserve">Bearing housing temperature exceeds normal range [Y/N] </t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1400,49 +1400,49 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">OHE - Overheating </t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller fatigue crack propagates through shroud, creating leak path for process fluid </t>
+          <t xml:space="preserve">Ingress of contaminants into grease/lubricant increases frictional torque and temperature </t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller NDT crack detection [Y/N]; Pressure cycling monitoring [Y/N]; Crack propagation analysis [Y/N] </t>
+          <t xml:space="preserve">Bearing housing temperature exceeds normal range [Y/N] </t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1452,49 +1452,49 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller vane fractures from fatigue or impact causing sudden vibration spike and potential seizure </t>
+          <t xml:space="preserve">Wear of the bearing housing seal allows lubricating oil/grease to leak externally </t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration trip verification [Y/N]; Impeller crack detection NDT [Y/N]; Protective device function check [Y/N] </t>
+          <t xml:space="preserve">Oil/grease residue visible on bearing housing or surrounding area [Y/N] </t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1504,49 +1504,49 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Failure-Finding; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">ELU - External leakage - utility medium </t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking/Seizure </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Impeller locks against casing or wear ring due to clearance loss, foreign object, or thermal binding </t>
+          <t xml:space="preserve">Distortion of bearing housing sealing surfaces prevents proper sealing </t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Running clearance verification [Y/N]; Start-up procedure compliance check [Y/N]; Impeller visual inspection [Y/N] </t>
+          <t xml:space="preserve">Oil/grease residue visible on bearing housing or surrounding area [Y/N] </t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1556,49 +1556,49 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert kinetic energy to hydrodynamic energy for fluid transport at rated pressure and flow </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Impeller Failure</t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Convert rotational energy into fluid velocity and pressure </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack propagates to critical length causing impeller burst during operation </t>
+          <t xml:space="preserve">Increased bearing clearance due to wear alters shaft position, affecting monitoring parameters </t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue life calculation [Y/N]; Operating stress analysis [Y/N]; Material certification check [Y/N] </t>
+          <t xml:space="preserve">Bearing condition monitoring parameters deviate from baseline [Y/N] </t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1608,49 +1608,49 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>DE Bearing Failure *</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Supports and allows rotation of the pump shaft on the drive end, reducing friction and maintaining radial alignment </t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cyclic bending from misalignment or imbalance initiates shaft fatigue crack causing vibration </t>
+          <t xml:space="preserve">Contamination degrades lubricant properties, altering temperature and vibration trends </t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft NDT inspection [Y/N]; Vibration trend analysis [Y/N]; Operating load verification [Y/N] </t>
+          <t xml:space="preserve">Bearing condition monitoring parameters deviate from baseline [Y/N] </t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1660,29 +1660,29 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Thrust Bearing Failure (*)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Absorbs axial hydraulic thrust generated by the impeller, maintaining the rotor's axial position within the casing </t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1692,17 +1692,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/Alignment failure </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Driver-to-pump shaft misalignment induces bending moment and lateral vibration </t>
+          <t xml:space="preserve">Progressive degradation of thrust bearing pads increases axial clearance and vibration </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Laser alignment verification [Y/N]; Thermal growth compensation check [Y/N]; Bearing clearance measurement [Y/N] </t>
+          <t xml:space="preserve">Axial shaft position or vibration levels exceed limits [Y/N] </t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1712,29 +1712,29 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Thrust Bearing Failure (*)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Absorbs axial hydraulic thrust generated by the impeller, maintaining the rotor's axial position within the casing </t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1744,17 +1744,17 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose coupling fit or shaft key causes rotational imbalance and 1X RPM vibration </t>
+          <t xml:space="preserve">Contamination of lubricating oil causes abrasive wear on thrust bearing pads </t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Coupling hub torque verification [Y/N]; Key fit inspection [Y/N]; Shaft runout measurement [Y/N] </t>
+          <t xml:space="preserve">Axial shaft position or vibration levels exceed limits [Y/N] </t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1764,49 +1764,49 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Thrust Bearing Failure (*)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Absorbs axial hydraulic thrust generated by the impeller, maintaining the rotor's axial position within the casing </t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft thermal bow from uneven heating during standby or improper storage causes high vibration </t>
+          <t xml:space="preserve">Partial seizure of thrust bearing pads due to lubrication failure generates noise </t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft runout verification [Y/N]; Heat soak procedure check [Y/N]; Storage condition inspection [Y/N] </t>
+          <t xml:space="preserve">Audible rubbing or grinding noise from pump bearing area [Y/N] </t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1816,49 +1816,49 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Thrust Bearing Failure (*)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Absorbs axial hydraulic thrust generated by the impeller, maintaining the rotor's axial position within the casing </t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Permanent shaft bow from overheating or mishandling increases internal clearances, reducing pump efficiency </t>
+          <t xml:space="preserve">Continuous abrasive wear of thrust bearing pads creates a steady rubbing sound </t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft straightness measurement [Y/N]; Performance trend analysis [Y/N]; Clearance verification [Y/N] </t>
+          <t xml:space="preserve">Audible rubbing or grinding noise from pump bearing area [Y/N] </t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1868,49 +1868,49 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Thrust Bearing Failure (*)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Absorbs axial hydraulic thrust generated by the impeller, maintaining the rotor's axial position within the casing </t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">OHE - Overheating </t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft journal surface wear increases bearing clearance, reducing rotor stability and pump efficiency </t>
+          <t xml:space="preserve">Pad sticking causes excessive friction and a rapid localized temperature rise </t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft diameter measurement [Y/N]; Bearing clearance trend [Y/N]; Oil analysis for wear metals [Y/N] </t>
+          <t xml:space="preserve">High temperature reading from thrust bearing temperature probe [Y/N] </t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1920,49 +1920,49 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Thrust Bearing Failure (*)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Absorbs axial hydraulic thrust generated by the impeller, maintaining the rotor's axial position within the casing </t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">OHE - Overheating </t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft corrosion reduces cross-section area, increasing torsional deflection and affecting torque transmission </t>
+          <t xml:space="preserve">High frictional losses in a heavily loaded or worn thrust bearing generate heat </t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft surface inspection [Y/N]; Material verification [Y/N]; Corrosion monitoring [Y/N] </t>
+          <t xml:space="preserve">High temperature reading from thrust bearing temperature probe [Y/N] </t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1972,29 +1972,29 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Thrust Bearing Failure (*)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Absorbs axial hydraulic thrust generated by the impeller, maintaining the rotor's axial position within the casing </t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2004,17 +2004,17 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft surface erosion from contaminated fluid reduces diameter, affecting component fit and pump alignment </t>
+          <t xml:space="preserve">Axial rotor movement due to wear changes impeller-to-casing clearance, affecting performance </t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft diameter measurement [Y/N]; Fluid particle analysis [Y/N]; Shaft coating condition check [Y/N] </t>
+          <t xml:space="preserve">Axial shaft displacement exceeds operating limit [Y/N] </t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2024,49 +2024,49 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Thrust Bearing Failure (*)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Absorbs axial hydraulic thrust generated by the impeller, maintaining the rotor's axial position within the casing </t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack propagation in shaft emits acoustic emissions detectable during operation </t>
+          <t xml:space="preserve">Distortion of thrust bearing support structure alters axial clearance </t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic emission monitoring [Y/N]; Shaft NDT during overhaul [Y/N]; Vibration spectrum analysis [Y/N] </t>
+          <t xml:space="preserve">Axial shaft displacement exceeds operating limit [Y/N] </t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2076,49 +2076,49 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Pump Shaft Failure (*) *</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Transmits rotational torque from the coupling to the impeller, ensuring concentric rotation </t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking/Seizure </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft rubbing against stationary component due to deflection generates grinding/rubbing noise </t>
+          <t xml:space="preserve">Crack initiation and propagation from cyclic bending or torsional loads </t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Running clearance verification [Y/N]; Shaft deflection calculation [Y/N]; Bearing alignment check [Y/N] </t>
+          <t xml:space="preserve">High vibration alarms; potential for catastrophic shaft break [Y/N] </t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2128,49 +2128,49 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Pump Shaft Failure (*) *</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Transmits rotational torque from the coupling to the impeller, ensuring concentric rotation </t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debris-contaminated oil in shaft bearing clearance generates intermittent scratching noise </t>
+          <t xml:space="preserve">Permanent shaft bending due to overload, causing an unbalance condition </t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oil sample analysis [Y/N]; Shaft surface inspection [Y/N]; Oil filter condition check [Y/N] </t>
+          <t xml:space="preserve">High vibration alarms; potential for catastrophic shaft break [Y/N] </t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2180,49 +2180,49 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Pump Shaft Failure (*) *</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Transmits rotational torque from the coupling to the impeller, ensuring concentric rotation </t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn shaft journal increases friction with bearing material, generating frictional heat in bearing zone </t>
+          <t xml:space="preserve">Corrosion reduces the shaft's fatigue strength, leading to vibration and eventual failure </t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft journal inspection [Y/N]; Bearing temperature monitoring [Y/N]; Oil thermal analysis [Y/N] </t>
+          <t xml:space="preserve">High vibration alarms; potential for catastrophic shaft break [Y/N] </t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2232,49 +2232,49 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Pump Shaft Failure (*) *</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Transmits rotational torque from the coupling to the impeller, ensuring concentric rotation </t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking/Seizure </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal growth exceeds available clearance causing shaft-to-stationary contact and runaway heating </t>
+          <t xml:space="preserve">A propagating fatigue crack generates periodic mechanical noise as it opens and closes under load </t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal growth calculation [Y/N]; Pump temperature monitoring [Y/N]; Clearance design verification [Y/N] </t>
+          <t xml:space="preserve">Audible cyclical clicking or knocking noise from the pump [Y/N] </t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2284,49 +2284,49 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Pump Shaft Failure (*) *</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Transmits rotational torque from the coupling to the impeller, ensuring concentric rotation </t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contaminated lubricant increases shaft journal friction coefficient, generating excess bearing area heat </t>
+          <t xml:space="preserve">Rubbing of a bent shaft against stationary internal components </t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oil sample analysis [Y/N]; Seal condition check [Y/N]; Contamination source identification [Y/N] </t>
+          <t xml:space="preserve">Audible cyclical clicking or knocking noise from the pump [Y/N] </t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2336,49 +2336,49 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Pump Shaft Failure (*) *</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Transmits rotational torque from the coupling to the impeller, ensuring concentric rotation </t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft surface wear damages oil seal contact area, allowing lube oil leak from bearing housing </t>
+          <t xml:space="preserve">A fatigue crack propagates to the outside of the containment area, causing a leak </t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft surface inspection at seal location [Y/N]; Oil leak rate monitoring [Y/N]; Bearing housing pressure check [Y/N] </t>
+          <t xml:space="preserve">Process fluid leak from pump shaft seal area or casing joint [Y/N] </t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2388,49 +2388,49 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Pump Shaft Failure (*) *</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Transmits rotational torque from the coupling to the impeller, ensuring concentric rotation </t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft surface deformation at seal contact area creates gap for oil leakage past seal element </t>
+          <t xml:space="preserve">Localized corrosion pitting on the shaft creates a leak path </t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft runout measurement at seal location [Y/N]; Seal housing alignment check [Y/N]; Shaft surface finish verification [Y/N] </t>
+          <t xml:space="preserve">Process fluid leak from pump shaft seal area or casing joint [Y/N] </t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2440,49 +2440,49 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Pump Shaft Failure (*) *</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Transmits rotational torque from the coupling to the impeller, ensuring concentric rotation </t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft corrosion at seal contact area creates pitted surface allowing oil bypass past seal lip </t>
+          <t xml:space="preserve">Catastrophic shaft fracture due to fatigue, corrosion fatigue, or instantaneous overload </t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft surface corrosion inspection [Y/N]; Corrosion protection verification [Y/N]; Material upgrade evaluation [Y/N] </t>
+          <t xml:space="preserve">Pump stops rotating; loss of flow and pressure [Y/N] </t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2492,29 +2492,29 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Redesign </t>
+          <t xml:space="preserve">Run-to-Failure </t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Pump Shaft Failure (*) *</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Transmits rotational torque from the coupling to the impeller, ensuring concentric rotation </t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2524,17 +2524,17 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Complete shaft fracture from fatigue crack propagation; pump loses all torque transmission capability </t>
+          <t xml:space="preserve">Shaft seizes within bearing or wearing rings due to loss of clearance or lubrication </t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft material certification check [Y/N]; Vibration shutdown test [Y/N]; Overload protection verification [Y/N] </t>
+          <t xml:space="preserve">Pump stops rotating; loss of flow and pressure [Y/N] </t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2544,49 +2544,49 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Failure-Finding; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Pump Shaft Failure (*) *</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Transmits rotational torque from the coupling to the impeller, ensuring concentric rotation </t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking/Seizure </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft seizes in bearing due to lubrication failure; pump rotor locks and driver trips </t>
+          <t xml:space="preserve">A slightly bent shaft causes the impeller to run out of position, affecting performance </t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication system flow check [Y/N]; Bearing temperature trend analysis [Y/N]; Trip system verification [Y/N] </t>
+          <t xml:space="preserve">Pump performance (differential pressure vs. flow) has degraded [Y/N] </t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2596,49 +2596,49 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Failure-Finding </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit rotational torque from driver to impeller </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shaft Failure</t>
+          <t>Pump Shaft Failure (*) *</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transmit torque from coupling to impeller while supporting radial and axial loads </t>
+          <t xml:space="preserve">Transmits rotational torque from the coupling to the impeller, ensuring concentric rotation </t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft fatigue crack reaches critical size during operation; sudden fracture occurs under normal torque </t>
+          <t xml:space="preserve">Corrosion leads to permanent loss of material, affecting impeller position </t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack growth monitoring [Y/N]; Operating stress reduction assessment [Y/N]; Shaft replacement interval [Y/N] </t>
+          <t xml:space="preserve">Pump performance (differential pressure vs. flow) has degraded [Y/N] </t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2648,49 +2648,49 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Redesign; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face wear from normal operation exceeds wear limit, creating leak path for process fluid </t>
+          <t xml:space="preserve">Material loss on vanes due to fluid abrasion, causing mass unbalance </t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face wear measurement [Y/N]; Leak rate monitoring [Y/N]; Seal life tracking [Y/N] </t>
+          <t xml:space="preserve">Pump vibration levels increase [Y/N] </t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2700,49 +2700,49 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.1 Cavitation </t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Secondary seal elastomer fatigue from thermal cycling causes loss of sealing force and leakage </t>
+          <t xml:space="preserve">Cavitation pitting causes localized material loss and unbalance, leading to high vibration </t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elastomer condition inspection [Y/N]; Seal flush system operation check [Y/N]; Thermal cycle monitoring [Y/N] </t>
+          <t xml:space="preserve">Pump vibration levels increase [Y/N] </t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2752,49 +2752,49 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/Alignment failure </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shaft-to-seal housing misalignment causes uneven face loading and localized seal face separation </t>
+          <t xml:space="preserve">Uneven corrosion of the impeller surface creates mass unbalance </t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump alignment verification [Y/N]; Seal face contact pattern check [Y/N]; Shaft runout measurement [Y/N] </t>
+          <t xml:space="preserve">Pump vibration levels increase [Y/N] </t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2804,49 +2804,49 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP - External leakage - process medium </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.1 Cavitation </t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal drive mechanism loose causes seal face separation and sudden large process fluid leak </t>
+          <t xml:space="preserve">Collapse of vapor bubbles causes a crackling or rattling noise </t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal drive torque verification [Y/N]; Seal visual inspection [Y/N]; Installation procedure review [Y/N] </t>
+          <t xml:space="preserve">Audible noise from the pump casing [Y/N] </t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2856,49 +2856,49 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face wear increases internal leakage across seal faces, reducing pump volumetric efficiency </t>
+          <t xml:space="preserve">Rubbing of the impeller against the casing or wear rings produces a metallic noise </t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal leakage rate trending [Y/N]; Pump performance check [Y/N]; Seal consumption benchmarking [Y/N] </t>
+          <t xml:space="preserve">Audible noise from the pump casing [Y/N] </t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2908,49 +2908,49 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal metal bellows or hardware corrosion degrades spring force, affecting seal face closing force </t>
+          <t xml:space="preserve">Flow turbulence caused by eroded vanes generates hydraulic noise </t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Material compatibility verification [Y/N]; Process fluid analysis [Y/N]; Seal condition inspection [Y/N] </t>
+          <t xml:space="preserve">Audible noise from the pump casing [Y/N] </t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2960,29 +2960,29 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2997,12 +2997,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face erosion from abrasive particles increases internal leakage and reduces pump efficiency </t>
+          <t xml:space="preserve">Erosion reduces the impeller's ability to impart energy, decreasing head and flow </t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fluid particle analysis [Y/N]; Seal face condition check [Y/N]; Flush system filter inspection [Y/N] </t>
+          <t xml:space="preserve">Pump discharge pressure and flow rate below required operating point [Y/N] </t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3012,29 +3012,29 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face thermal distortion creates wavy contact pattern, increasing leakage and degrading performance </t>
+          <t xml:space="preserve">Corrosion changes the impeller geometry and surface finish, leading to performance degradation </t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face flatness measurement [Y/N]; Operating temperature check [Y/N]; Cooling system adequacy verification [Y/N] </t>
+          <t xml:space="preserve">Pump discharge pressure and flow rate below required operating point [Y/N] </t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3064,49 +3064,49 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">5.1 Blockage/plugged </t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face frictional wear generates heat, raising seal chamber temperature beyond normal operating range </t>
+          <t xml:space="preserve">A foreign object partially blocking the impeller vane passages reduces flow </t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal temperature monitoring [Y/N]; Flush system flow verification [Y/N]; Seal face wear measurement [Y/N] </t>
+          <t xml:space="preserve">Pump discharge pressure and flow rate below required operating point [Y/N] </t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3116,49 +3116,49 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">VLO - Very low output </t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.1 Leakage </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flush system leakage reduces seal cooling flow causing face overheating and thermal cracking </t>
+          <t xml:space="preserve">Severe erosion destroys the impeller geometry, causing near-complete loss of pumping ability </t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flush line integrity check [Y/N]; Flush flow rate monitoring [Y/N]; Seal chamber pressure check [Y/N] </t>
+          <t xml:space="preserve">Pump runs but produces negligible flow and pressure [Y/N] </t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3168,49 +3168,49 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Run-to-Failure </t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">VLO - Very low output </t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.1 Blockage/plugged </t>
+          <t xml:space="preserve">2.1 Cavitation </t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal flush line blockage starves seal faces of cooling flow, causing rapid temperature rise </t>
+          <t xml:space="preserve">Massive cavitation damage destroys the impeller geometry </t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flush line inspection [Y/N]; Flush system pressure check [Y/N]; Filter condition monitoring [Y/N] </t>
+          <t xml:space="preserve">Pump runs but produces negligible flow and pressure [Y/N] </t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3220,49 +3220,49 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Run-to-Failure </t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contaminated flush fluid deposits on seal faces increases friction, generating excess heat </t>
+          <t xml:space="preserve">Impeller fractures due to a crack or manufacturing defect </t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flush fluid quality analysis [Y/N]; Seal face deposit inspection [Y/N]; Flush filter replacement [Y/N] </t>
+          <t xml:space="preserve">Pump stops rotating; immediate loss of flow and pressure [Y/N] </t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3272,49 +3272,49 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Run-to-Failure </t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal dry running due to flush failure generates high-frequency squealing/screeching noise </t>
+          <t xml:space="preserve">Impeller seizes against the casing due to a large foreign object or severe misalignment </t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flush system operational check [Y/N]; Dry run protection test [Y/N]; Acoustic seal monitoring [Y/N] </t>
+          <t xml:space="preserve">Pump stops rotating; immediate loss of flow and pressure [Y/N] </t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3324,49 +3324,49 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Failure-Finding; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">OHE - Overheating </t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 Cavitation </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face cavitation from fluid vaporization between faces generates popping/gurgling noises </t>
+          <t xml:space="preserve">Excessive rubbing of the impeller against the casing generates friction and heat </t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal chamber pressure verification [Y/N]; Flush pressure check [Y/N]; Seal face inspection [Y/N] </t>
+          <t xml:space="preserve">Pump casing temperature exceeds normal range [Y/N] </t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3376,49 +3376,49 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Impeller Failure (*)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Imparts kinetic energy to the fluid, converting it to pressure head as the fluid exits the volute </t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">OHE - Overheating </t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">5.1 Blockage/plugged </t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loose seal drive components create rattling noise during pump rotation </t>
+          <t xml:space="preserve">A partially blocked impeller causes high fluid shear and energy dissipation, manifesting as heat </t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal drive mechanism torque check [Y/N]; Seal component tightness verification [Y/N]; Installation quality audit [Y/N] </t>
+          <t xml:space="preserve">Pump casing temperature exceeds normal range [Y/N] </t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3428,49 +3428,49 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Pump Casing Failure (*) *</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Contains the pressurized process fluid and provides a volute to convert kinetic energy to pressure </t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Non-uniform seal face wear creates out-of-plane condition inducing vibration in seal assembly </t>
+          <t xml:space="preserve">Corrosion thins the casing wall, leading to a through-wall pinhole or crack </t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face runout measurement [Y/N]; Vibration monitoring at seal housing [Y/N]; Wear pattern analysis [Y/N] </t>
+          <t xml:space="preserve">Process fluid drip or spray from pump casing [Y/N] </t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3480,49 +3480,49 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Pump Casing Failure (*) *</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Contains the pressurized process fluid and provides a volute to convert kinetic energy to pressure </t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/Alignment failure </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misaligned seal components create rotational imbalance and seal-induced vibration </t>
+          <t xml:space="preserve">A crack at casing stress concentration points (e.g., nozzle junctions) </t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal housing concentricity check [Y/N]; Shaft alignment verification [Y/N]; Installation procedure validation [Y/N] </t>
+          <t xml:space="preserve">Process fluid drip or spray from pump casing [Y/N] </t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3532,49 +3532,49 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Pump Casing Failure (*) *</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Contains the pressurized process fluid and provides a volute to convert kinetic energy to pressure </t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face waviness from thermal fatigue creates intermittent contact and vibration </t>
+          <t xml:space="preserve">Internal erosion from high-velocity fluid or cavitation thins the casing wall </t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face flatness measurement [Y/N]; Thermal cycling analysis [Y/N]; Vibration trending [Y/N] </t>
+          <t xml:space="preserve">Process fluid drip or spray from pump casing [Y/N] </t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3584,49 +3584,49 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Pump Casing Failure (*) *</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Contains the pressurized process fluid and provides a volute to convert kinetic energy to pressure </t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal face catastrophic fracture from thermal shock or pressure excursion causes sudden massive leak </t>
+          <t xml:space="preserve">General corrosion reduces wall thickness below minimum design requirements </t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal operating limits verification [Y/N]; Pressure surge protection check [Y/N]; Start-up procedure compliance [Y/N] </t>
+          <t xml:space="preserve">UT inspection indicates wall thickness below minimum allowable [Y/N] </t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3636,49 +3636,49 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Failure-Finding; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Pump Casing Failure (*) *</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Contains the pressurized process fluid and provides a volute to convert kinetic energy to pressure </t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking/Seizure </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal faces stick together during shutdown due to coking/polymerization; shaft start tears seal faces apart </t>
+          <t xml:space="preserve">A fatigue crack compromises the structural integrity of the casing </t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anti-seize procedure during prolonged shutdown [Y/N]; Seal face cleaning during maintenance [Y/N]; Process fluid coking tendency monitoring [Y/N] </t>
+          <t xml:space="preserve">NDT or visual inspection indicates a crack in the casing [Y/N] </t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3688,49 +3688,49 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prevent process fluid leakage along rotating shaft to atmosphere </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Mechanical Seal Failure</t>
+          <t>Pump Casing Failure (*) *</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal rotating shaft penetration through pump casing to prevent process fluid leak </t>
+          <t xml:space="preserve">Contains the pressurized process fluid and provides a volute to convert kinetic energy to pressure </t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">FWR - Failure while running </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal retaining hardware loosens during operation causing face separation and sudden catastrophic leak </t>
+          <t xml:space="preserve">Internal pitting creates turbulent flow paths, slightly altering pump hydraulics </t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seal hardware lock-tightening verification [Y/N]; Vibration-induced loosening check [Y/N]; Seal assembly torque audit [Y/N] </t>
+          <t xml:space="preserve">Pump differential pressure/flow deviates from OEM curve [Y/N] </t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3740,49 +3740,49 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Pump Casing Failure (*) *</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Contains the pressurized process fluid and provides a volute to convert kinetic energy to pressure </t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB - Vibration </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing rolling element and raceway wear increases radial clearance causing shaft movement and vibration </t>
+          <t xml:space="preserve">Thermal or pressure stress distorts the volute, changing flow path geometry </t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing clearance measurement [Y/N]; Vibration velocity monitoring [Y/N]; Wear particle analysis [Y/N] </t>
+          <t xml:space="preserve">Pump differential pressure/flow deviates from OEM curve [Y/N] </t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3792,29 +3792,29 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Pump Casing Failure (*) *</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Contains the pressurized process fluid and provides a volute to convert kinetic energy to pressure </t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -3824,17 +3824,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.3 Clearance/Alignment failure </t>
+          <t xml:space="preserve">2.1 Cavitation </t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing housing misalignment causes uneven roller loading, leading to localized wear and vibration </t>
+          <t xml:space="preserve">Cavitation damage to the internal surfaces can cause hydraulic unbalance </t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Housing alignment check [Y/N]; Shaft alignment verification [Y/N]; Bearing fit clearance check [Y/N] </t>
+          <t xml:space="preserve">Casing vibration levels exceed alarm limits [Y/N] </t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3844,29 +3844,29 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Pump Casing Failure (*) *</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Contains the pressurized process fluid and provides a volute to convert kinetic energy to pressure </t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3876,17 +3876,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Subsurface fatigue initiates raceway spalling; spall progression generates increasing vibration amplitude </t>
+          <t xml:space="preserve">Loose casing hold-down bolts allow the assembly to vibrate </t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration enveloping monitoring [Y/N]; Bearing life tracking [Y/N]; Oil analysis for bearing metals [Y/N] </t>
+          <t xml:space="preserve">Casing vibration levels exceed alarm limits [Y/N] </t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3896,29 +3896,29 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Wearing Rings Failure (*) *</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Provide a close-clearance seal between the impeller and casing to reduce internal recirculation and maintain efficiency </t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3928,17 +3928,17 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contaminated lubricant causes abrasive wear damage to bearing surfaces, generating progressive vibration </t>
+          <t xml:space="preserve">Increased clearance from wear allows rotor-dynamic instabilities and vibration </t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oil cleanliness analysis [Y/N]; Bearing housing seal check [Y/N]; Lubricant filtration condition [Y/N] </t>
+          <t xml:space="preserve">Pump vibration levels increase [Y/N] </t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3948,49 +3948,49 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Wearing Rings Failure (*) *</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Provide a close-clearance seal between the impeller and casing to reduce internal recirculation and maintain efficiency </t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn bearing rolling elements produce low-frequency rumbling noise during rotation </t>
+          <t xml:space="preserve">Insufficient clearance causing rubbing between impeller and casing rings </t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ultrasonic bearing inspection [Y/N]; Bearing sound level check [Y/N]; Lubricant condition verification [Y/N] </t>
+          <t xml:space="preserve">Pump vibration levels increase [Y/N] </t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4000,49 +4000,49 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Wearing Rings Failure (*) *</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Provide a close-clearance seal between the impeller and casing to reduce internal recirculation and maintain efficiency </t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue spalling generates clicking/grinding noise as rollers pass over damaged raceway </t>
+          <t xml:space="preserve">Increased clearance allows higher internal recirculation, reducing pump efficiency </t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acoustic emission monitoring [Y/N]; Bearing replacement interval check [Y/N]; Vibration spectrum analysis [Y/N] </t>
+          <t xml:space="preserve">Pump performance (differential pressure vs. flow) has degraded [Y/N] </t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4052,49 +4052,49 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Wearing Rings Failure (*) *</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Provide a close-clearance seal between the impeller and casing to reduce internal recirculation and maintain efficiency </t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI - Noise </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Debris-contaminated lubricant causes abrasive wear noise in bearing rolling elements </t>
+          <t xml:space="preserve">Erosion enlarges the gap between the rings, increasing recirculation and reducing efficiency </t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oil sample analysis [Y/N]; Bearing housing seal inspection [Y/N]; Contamination source investigation [Y/N] </t>
+          <t xml:space="preserve">Pump performance (differential pressure vs. flow) has degraded [Y/N] </t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4104,49 +4104,49 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Wearing Rings Failure (*) *</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Provide a close-clearance seal between the impeller and casing to reduce internal recirculation and maintain efficiency </t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing wear generates frictional heat raising bearing housing temperature above normal </t>
+          <t xml:space="preserve">Seizure of the impeller in the casing due to galled or worn wearing rings </t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing clearance trend check [Y/N]; Temperature trend analysis [Y/N]; Oil thermal degradation check [Y/N] </t>
+          <t xml:space="preserve">Pump seizes or requires excessive torque to rotate [Y/N] </t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4156,49 +4156,49 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Wearing Rings Failure (*) *</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Provide a close-clearance seal between the impeller and casing to reduce internal recirculation and maintain efficiency </t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.6 Sticking/Seizure </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubricant starvation causes metal-to-metal contact, friction heat spike, and rapid temperature rise </t>
+          <t xml:space="preserve">Fracture of a wearing ring can lodge it between the impeller and casing </t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubrication system flow verification [Y/N]; Bearing temperature monitoring [Y/N]; Grease/oil level check [Y/N] </t>
+          <t xml:space="preserve">Pump seizes or requires excessive torque to rotate [Y/N] </t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4208,49 +4208,49 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Run-to-Failure </t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Wearing Rings Failure (*) *</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Provide a close-clearance seal between the impeller and casing to reduce internal recirculation and maintain efficiency </t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contaminated grease/oil increases internal bearing friction generating excess heat </t>
+          <t xml:space="preserve">Rubbing of the impeller against the casing rings produces a metallic noise </t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubricant condition analysis [Y/N]; Bearing housing vent check [Y/N]; Bearing flush procedure [Y/N] </t>
+          <t xml:space="preserve">Audible metallic rubbing or grinding noise from the pump [Y/N] </t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -4260,49 +4260,49 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Wearing Rings Failure (*) *</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Provide a close-clearance seal between the impeller and casing to reduce internal recirculation and maintain efficiency </t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE - Overheating </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">1.6 Sticking </t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue spalling increases rolling resistance, converting mechanical energy to heat in bearing zone </t>
+          <t xml:space="preserve">Intermittent sticking of the rings due to galling generates periodic noises </t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing fatigue life tracking [Y/N]; Temperature trend with vibration correlation [Y/N]; Bearing replacement at life limit [Y/N] </t>
+          <t xml:space="preserve">Audible metallic rubbing or grinding noise from the pump [Y/N] </t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -4312,49 +4312,49 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Coupling Failure</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Transmits rotational torque from the driver shaft to the pump shaft </t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing seal lip wear allows lubricating oil to leak past seal to pump exterior </t>
+          <t xml:space="preserve">Misalignment between driver and pump shafts generates forces that excite vibration </t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing seal condition inspection [Y/N]; Oil leak rate monitoring [Y/N]; Bearing housing pressure check [Y/N] </t>
+          <t xml:space="preserve">High vibration readings at the pump drive end bearing housing [Y/N] </t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -4364,49 +4364,49 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Coupling Failure</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Transmits rotational torque from the driver shaft to the pump shaft </t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELU - External leakage - utility medium </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.4 Wear </t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing housing face distortion from overtightening creates leak path for oil past gasket </t>
+          <t xml:space="preserve">Wear of coupling flexible elements (spider, grid, or discs) causes unbalance and vibration </t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Housing bolt torque verification [Y/N]; Housing face flatness check [Y/N]; Gasket condition inspection [Y/N] </t>
+          <t xml:space="preserve">High vibration readings at the pump drive end bearing housing [Y/N] </t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -4416,34 +4416,34 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Coupling Failure</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Transmits rotational torque from the driver shaft to the pump shaft </t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Worn bearing increases rotor radial displacement, affecting impeller-to-casing concentricity and pump performance </t>
+          <t xml:space="preserve">Worn coupling elements produce a cyclical noise as they transmit torque </t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing clearance trend analysis [Y/N]; Pump performance monitoring [Y/N]; Rotor position measurement [Y/N] </t>
+          <t xml:space="preserve">Audible noise from the coupling guard area [Y/N] </t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4468,49 +4468,49 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Coupling Failure</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Transmits rotational torque from the driver shaft to the pump shaft </t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.2 Contamination </t>
+          <t xml:space="preserve">1.5 Looseness </t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lubricant contamination accelerates bearing wear, increasing clearance and degrading pump efficiency </t>
+          <t xml:space="preserve">Worn keys or splines in the coupling cause a clicking or knocking noise as shafts rotate </t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oil contamination analysis [Y/N]; Bearing housing seal check [Y/N]; Filter condition monitoring [Y/N] </t>
+          <t xml:space="preserve">Audible noise from the coupling guard area [Y/N] </t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4520,49 +4520,49 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Coupling Failure</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load and maintain shaft radial position at pump non-drive end </t>
+          <t xml:space="preserve">Transmits rotational torque from the driver shaft to the pump shaft </t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE - Parameter deviation </t>
+          <t xml:space="preserve">FWR - Failure while running </t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.5 Breakage </t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing fatigue increases internal clearance, altering shaft position and reducing pump hydraulic efficiency </t>
+          <t xml:space="preserve">Fatigue or catastrophic failure of the coupling element, causing complete torque transmission loss </t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bearing fatigue monitoring [Y/N]; Shaft position measurement [Y/N]; Performance degradation trend [Y/N] </t>
+          <t xml:space="preserve">Pump stops rotating, driver continues running; loss of flow [Y/N] </t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4572,37 +4572,189 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Predictive; Predictive </t>
+          <t xml:space="preserve">Run-to-Failure </t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pump Centrifugal </t>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support radial load at non-drive end of pump rotor </t>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NDE Bearing Failure *</t>
+          <t>Coupling Failure</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Support radial load and maintain shaft radial position</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
+          <t xml:space="preserve">Transmits rotational torque from the driver shaft to the pump shaft </t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FWR - Failure while running </t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coupling hub slips on the shaft due to a loose key/taper lock, resulting in loss of torque transmission </t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pump stops rotating, driver continues running; loss of flow [Y/N] </t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Coupling Failure</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transmits rotational torque from the driver shaft to the pump shaft </t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.5 Breakage </t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coupling is already fractured, preventing torque transmission at startup </t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver starts but pump does not rotate; no flow [Y/N] </t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Run-to-Failure </t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transport fluids at a rated pressure and flow by converting kinetic energy to hydrodynamic energy </t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Coupling Failure</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Transmits rotational torque from the driver shaft to the pump shaft </t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FTS - Failure to start on demand </t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coupling hub has slipped on the shaft, creating a clearance that prevents torque transfer at startup </t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Driver starts but pump does not rotate; no flow [Y/N] </t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUCE - Pump Centrifugal </t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Transport fluids at a rated pressure and</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>nan *</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
